--- a/proposed/results/training_tables/urban_training_results.xlsx
+++ b/proposed/results/training_tables/urban_training_results.xlsx
@@ -448,10 +448,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>12535.3253</v>
+        <v>11539.6105</v>
       </c>
       <c r="C2" t="n">
-        <v>250.7065</v>
+        <v>230.7922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.5936</v>
+        <v>4.2038</v>
       </c>
     </row>
     <row r="3">
@@ -467,10 +467,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>6914.8955</v>
+        <v>4423.9677</v>
       </c>
       <c r="C3" t="n">
-        <v>138.2979</v>
+        <v>88.4794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0563</v>
+        <v>0.0692</v>
       </c>
     </row>
     <row r="4">
@@ -486,10 +486,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>9010.5808</v>
+        <v>6341.6193</v>
       </c>
       <c r="C4" t="n">
-        <v>180.2116</v>
+        <v>126.8324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0559</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>8940.4231</v>
+        <v>5948.323</v>
       </c>
       <c r="C5" t="n">
-        <v>178.8085</v>
+        <v>118.9665</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0532</v>
+        <v>0.06370000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8489.163</v>
+        <v>4965.6799</v>
       </c>
       <c r="C6" t="n">
-        <v>169.7833</v>
+        <v>99.31359999999999</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1409</v>
+        <v>0.2427</v>
       </c>
     </row>
     <row r="7">
@@ -543,10 +543,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>10164.6489</v>
+        <v>8067.5489</v>
       </c>
       <c r="C7" t="n">
-        <v>203.293</v>
+        <v>161.351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.0518</v>
+        <v>0.09379999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -562,10 +562,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>8389.882900000001</v>
+        <v>5889.6937</v>
       </c>
       <c r="C8" t="n">
-        <v>167.7977</v>
+        <v>117.7939</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0521</v>
+        <v>0.07049999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -581,10 +581,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>10000.7154</v>
+        <v>7338.9892</v>
       </c>
       <c r="C9" t="n">
-        <v>200.0143</v>
+        <v>146.7798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0505</v>
+        <v>0.0659</v>
       </c>
     </row>
     <row r="10">
@@ -600,10 +600,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>8119.8345</v>
+        <v>4418.3163</v>
       </c>
       <c r="C10" t="n">
-        <v>162.3967</v>
+        <v>88.3663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.147</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="11">
@@ -619,10 +619,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>11840.8564</v>
+        <v>8789.2641</v>
       </c>
       <c r="C11" t="n">
-        <v>236.8171</v>
+        <v>175.7853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.059</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="12">
@@ -638,10 +638,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>8124.6801</v>
+        <v>4176.7707</v>
       </c>
       <c r="C12" t="n">
-        <v>162.4936</v>
+        <v>83.5354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.0526</v>
+        <v>0.0835</v>
       </c>
     </row>
     <row r="13">
@@ -657,10 +657,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>10246.1368</v>
+        <v>4737.6156</v>
       </c>
       <c r="C13" t="n">
-        <v>204.9227</v>
+        <v>94.75230000000001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.0526</v>
+        <v>0.08740000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -676,10 +676,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>14273.2995</v>
+        <v>12481.3995</v>
       </c>
       <c r="C14" t="n">
-        <v>285.466</v>
+        <v>249.628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.1526</v>
+        <v>0.2637</v>
       </c>
     </row>
     <row r="15">
@@ -695,10 +695,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>7328.9381</v>
+        <v>3477.0225</v>
       </c>
       <c r="C15" t="n">
-        <v>146.5788</v>
+        <v>69.54040000000001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.0519</v>
+        <v>0.0771</v>
       </c>
     </row>
     <row r="16">
@@ -714,10 +714,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>10198.9395</v>
+        <v>6404.9654</v>
       </c>
       <c r="C16" t="n">
-        <v>203.9788</v>
+        <v>128.0993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.0542</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="17">
@@ -733,10 +733,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>12687.9159</v>
+        <v>10187.9159</v>
       </c>
       <c r="C17" t="n">
-        <v>253.7583</v>
+        <v>203.7583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0515</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -752,10 +752,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>8042.889</v>
+        <v>4940.7221</v>
       </c>
       <c r="C18" t="n">
-        <v>160.8578</v>
+        <v>98.81440000000001</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.1715</v>
+        <v>0.2377</v>
       </c>
     </row>
     <row r="19">
@@ -771,10 +771,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>8180.1863</v>
+        <v>5378.3178</v>
       </c>
       <c r="C19" t="n">
-        <v>163.6037</v>
+        <v>107.5664</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.059</v>
+        <v>0.0809</v>
       </c>
     </row>
     <row r="20">
@@ -790,10 +790,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>8105.7462</v>
+        <v>4403.2418</v>
       </c>
       <c r="C20" t="n">
-        <v>162.1149</v>
+        <v>88.06480000000001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0559</v>
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -809,10 +809,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>9819.573</v>
+        <v>7096.8255</v>
       </c>
       <c r="C21" t="n">
-        <v>196.3915</v>
+        <v>141.9365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -828,10 +828,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>10574.1742</v>
+        <v>7516.9116</v>
       </c>
       <c r="C22" t="n">
-        <v>211.4835</v>
+        <v>150.3382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.168</v>
+        <v>0.2319</v>
       </c>
     </row>
     <row r="23">
@@ -847,10 +847,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>9172.966200000001</v>
+        <v>3137.9777</v>
       </c>
       <c r="C23" t="n">
-        <v>183.4593</v>
+        <v>62.7596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0485</v>
+        <v>0.07489999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -866,10 +866,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>8494.7189</v>
+        <v>5540.0645</v>
       </c>
       <c r="C24" t="n">
-        <v>169.8944</v>
+        <v>110.8013</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.0521</v>
+        <v>0.0522</v>
       </c>
     </row>
     <row r="25">
@@ -885,10 +885,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>11050.0376</v>
+        <v>9228.1376</v>
       </c>
       <c r="C25" t="n">
-        <v>221.0008</v>
+        <v>184.5628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0519</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="26">
@@ -904,10 +904,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>11245.6459</v>
+        <v>8745.6459</v>
       </c>
       <c r="C26" t="n">
-        <v>224.9129</v>
+        <v>174.9129</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.1611</v>
+        <v>0.1891</v>
       </c>
     </row>
     <row r="27">
@@ -923,10 +923,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>9121.014999999999</v>
+        <v>6420.0367</v>
       </c>
       <c r="C27" t="n">
-        <v>182.4203</v>
+        <v>128.4007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.0516</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="28">
@@ -942,10 +942,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>13674.7571</v>
+        <v>11313.9571</v>
       </c>
       <c r="C28" t="n">
-        <v>273.4951</v>
+        <v>226.2791</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.0556</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="29">
@@ -961,10 +961,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>13025.5413</v>
+        <v>7745.1013</v>
       </c>
       <c r="C29" t="n">
-        <v>260.5108</v>
+        <v>154.902</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.0527</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="30">
@@ -980,10 +980,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>10377.6422</v>
+        <v>7023.7629</v>
       </c>
       <c r="C30" t="n">
-        <v>207.5528</v>
+        <v>140.4753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.1492</v>
+        <v>0.1798</v>
       </c>
     </row>
     <row r="31">
@@ -999,10 +999,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>7766.3806</v>
+        <v>3813.7125</v>
       </c>
       <c r="C31" t="n">
-        <v>155.3276</v>
+        <v>76.27419999999999</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0494</v>
+        <v>0.0614</v>
       </c>
     </row>
     <row r="32">
@@ -1018,10 +1018,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>10894.4866</v>
+        <v>8143.5232</v>
       </c>
       <c r="C32" t="n">
-        <v>217.8897</v>
+        <v>162.8705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.0552</v>
+        <v>0.06270000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1037,10 +1037,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>12702.5429</v>
+        <v>10819.6429</v>
       </c>
       <c r="C33" t="n">
-        <v>254.0509</v>
+        <v>216.3929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0538</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="34">
@@ -1056,10 +1056,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>7650.2696</v>
+        <v>3387.2365</v>
       </c>
       <c r="C34" t="n">
-        <v>153.0054</v>
+        <v>67.74469999999999</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.1536</v>
+        <v>0.1879</v>
       </c>
     </row>
     <row r="35">
@@ -1075,10 +1075,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>7373.7611</v>
+        <v>3371.1025</v>
       </c>
       <c r="C35" t="n">
-        <v>147.4752</v>
+        <v>67.4221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.0543</v>
+        <v>0.0706</v>
       </c>
     </row>
     <row r="36">
@@ -1094,10 +1094,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>9459.5782</v>
+        <v>5995.8568</v>
       </c>
       <c r="C36" t="n">
-        <v>189.1916</v>
+        <v>119.9171</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0528</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="37">
@@ -1113,10 +1113,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>7470.9626</v>
+        <v>4061.1305</v>
       </c>
       <c r="C37" t="n">
-        <v>149.4193</v>
+        <v>81.2226</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.0539</v>
+        <v>0.0694</v>
       </c>
     </row>
     <row r="38">
@@ -1132,10 +1132,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>8313.535400000001</v>
+        <v>5411.8609</v>
       </c>
       <c r="C38" t="n">
-        <v>166.2707</v>
+        <v>108.2372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.14</v>
+        <v>0.2021</v>
       </c>
     </row>
     <row r="39">
@@ -1151,10 +1151,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>7745.9688</v>
+        <v>3142.0282</v>
       </c>
       <c r="C39" t="n">
-        <v>154.9194</v>
+        <v>62.8406</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0536</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="40">
@@ -1170,10 +1170,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>8560.5913</v>
+        <v>5269.7545</v>
       </c>
       <c r="C40" t="n">
-        <v>171.2118</v>
+        <v>105.3951</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.0514</v>
+        <v>0.0721</v>
       </c>
     </row>
     <row r="41">
@@ -1189,10 +1189,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>7355.915</v>
+        <v>3791.0224</v>
       </c>
       <c r="C41" t="n">
-        <v>147.1183</v>
+        <v>75.82040000000001</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.0497</v>
+        <v>0.06909999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1208,10 +1208,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>8597.625400000001</v>
+        <v>5293.1785</v>
       </c>
       <c r="C42" t="n">
-        <v>171.9525</v>
+        <v>105.8636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.1505</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="43">
@@ -1227,10 +1227,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>9183.897499999999</v>
+        <v>4271.3124</v>
       </c>
       <c r="C43" t="n">
-        <v>183.6779</v>
+        <v>85.42619999999999</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.0493</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="44">
@@ -1246,10 +1246,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>9904.680700000001</v>
+        <v>5845.0168</v>
       </c>
       <c r="C44" t="n">
-        <v>198.0936</v>
+        <v>116.9003</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.0484</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="45">
@@ -1265,10 +1265,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>7674.2934</v>
+        <v>4031.6626</v>
       </c>
       <c r="C45" t="n">
-        <v>153.4859</v>
+        <v>80.63330000000001</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.0497</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="46">
@@ -1284,10 +1284,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>7501.601</v>
+        <v>3796.5991</v>
       </c>
       <c r="C46" t="n">
-        <v>150.032</v>
+        <v>75.932</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.1658</v>
+        <v>0.2182</v>
       </c>
     </row>
     <row r="47">
@@ -1303,10 +1303,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>11106.6766</v>
+        <v>6185.4564</v>
       </c>
       <c r="C47" t="n">
-        <v>222.1335</v>
+        <v>123.7091</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0644</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="48">
@@ -1322,10 +1322,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>8900.0607</v>
+        <v>5223.3494</v>
       </c>
       <c r="C48" t="n">
-        <v>178.0012</v>
+        <v>104.467</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.0496</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1341,10 +1341,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>13036.2075</v>
+        <v>11336.2075</v>
       </c>
       <c r="C49" t="n">
-        <v>260.7241</v>
+        <v>226.7241</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.0508</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="50">
@@ -1360,10 +1360,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>7849.5571</v>
+        <v>4125.5077</v>
       </c>
       <c r="C50" t="n">
-        <v>156.9911</v>
+        <v>82.5102</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.1542</v>
+        <v>0.2322</v>
       </c>
     </row>
     <row r="51">
@@ -1379,10 +1379,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>11496.7221</v>
+        <v>9635.3662</v>
       </c>
       <c r="C51" t="n">
-        <v>229.9344</v>
+        <v>192.7073</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.0579</v>
+        <v>0.0738</v>
       </c>
     </row>
     <row r="52">
@@ -1398,10 +1398,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>9228.315500000001</v>
+        <v>6477.6809</v>
       </c>
       <c r="C52" t="n">
-        <v>184.5663</v>
+        <v>129.5536</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0584</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="53">
@@ -1417,10 +1417,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>7540.301</v>
+        <v>3496.0265</v>
       </c>
       <c r="C53" t="n">
-        <v>150.806</v>
+        <v>69.9205</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0574</v>
+        <v>0.0658</v>
       </c>
     </row>
     <row r="54">
@@ -1436,10 +1436,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>11155.5603</v>
+        <v>8655.560299999999</v>
       </c>
       <c r="C54" t="n">
-        <v>223.1112</v>
+        <v>173.1112</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.1643</v>
+        <v>0.2161</v>
       </c>
     </row>
     <row r="55">
@@ -1455,10 +1455,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>7833.1608</v>
+        <v>3969.9714</v>
       </c>
       <c r="C55" t="n">
-        <v>156.6632</v>
+        <v>79.3994</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.0497</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="56">
@@ -1474,10 +1474,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>10360.779</v>
+        <v>7662.639</v>
       </c>
       <c r="C56" t="n">
-        <v>207.2156</v>
+        <v>153.2528</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0489</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="57">
@@ -1493,10 +1493,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>7468.7958</v>
+        <v>3435.1189</v>
       </c>
       <c r="C57" t="n">
-        <v>149.3759</v>
+        <v>68.7024</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.0481</v>
+        <v>0.0626</v>
       </c>
     </row>
     <row r="58">
@@ -1512,10 +1512,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>9334.193499999999</v>
+        <v>6122.341</v>
       </c>
       <c r="C58" t="n">
-        <v>186.6839</v>
+        <v>122.4468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.1411</v>
+        <v>0.2061</v>
       </c>
     </row>
     <row r="59">
@@ -1531,10 +1531,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>10719.2442</v>
+        <v>7877.2572</v>
       </c>
       <c r="C59" t="n">
-        <v>214.3849</v>
+        <v>157.5451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.0572</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="60">
@@ -1550,10 +1550,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>9124.145200000001</v>
+        <v>6595.7937</v>
       </c>
       <c r="C60" t="n">
-        <v>182.4829</v>
+        <v>131.9159</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.0622</v>
+        <v>0.0766</v>
       </c>
     </row>
     <row r="61">
@@ -1569,10 +1569,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>10891.9832</v>
+        <v>7798.8947</v>
       </c>
       <c r="C61" t="n">
-        <v>217.8397</v>
+        <v>155.9779</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.0569</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -1588,10 +1588,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>9021.596299999999</v>
+        <v>6470.0359</v>
       </c>
       <c r="C62" t="n">
-        <v>180.4319</v>
+        <v>129.4007</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1557</v>
+        <v>0.1953</v>
       </c>
     </row>
     <row r="63">
@@ -1607,10 +1607,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>9710.2394</v>
+        <v>7008.0103</v>
       </c>
       <c r="C63" t="n">
-        <v>194.2048</v>
+        <v>140.1602</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.0533</v>
+        <v>0.0626</v>
       </c>
     </row>
     <row r="64">
@@ -1626,10 +1626,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>8491.290300000001</v>
+        <v>5236.767</v>
       </c>
       <c r="C64" t="n">
-        <v>169.8258</v>
+        <v>104.7353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.0519</v>
+        <v>0.0641</v>
       </c>
     </row>
     <row r="65">
@@ -1645,10 +1645,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>8063.2742</v>
+        <v>3056.4649</v>
       </c>
       <c r="C65" t="n">
-        <v>161.2655</v>
+        <v>61.1293</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.0477</v>
+        <v>0.0565</v>
       </c>
     </row>
     <row r="66">
@@ -1664,10 +1664,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>8358.8519</v>
+        <v>4718.3755</v>
       </c>
       <c r="C66" t="n">
-        <v>167.177</v>
+        <v>94.36750000000001</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.1508</v>
+        <v>0.2232</v>
       </c>
     </row>
     <row r="67">
@@ -1683,10 +1683,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>13963.5652</v>
+        <v>11292.3841</v>
       </c>
       <c r="C67" t="n">
-        <v>279.2713</v>
+        <v>225.8477</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.0596</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -1702,10 +1702,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>9166.373</v>
+        <v>4602.7265</v>
       </c>
       <c r="C68" t="n">
-        <v>183.3275</v>
+        <v>92.0545</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.0589</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -1721,10 +1721,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>8187.8453</v>
+        <v>4480.6751</v>
       </c>
       <c r="C69" t="n">
-        <v>163.7569</v>
+        <v>89.6135</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.058</v>
+        <v>0.0682</v>
       </c>
     </row>
     <row r="70">
@@ -1740,10 +1740,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>10746.7822</v>
+        <v>7776.8018</v>
       </c>
       <c r="C70" t="n">
-        <v>214.9356</v>
+        <v>155.536</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.165</v>
+        <v>0.2124</v>
       </c>
     </row>
     <row r="71">
@@ -1759,10 +1759,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>8821.7127</v>
+        <v>5825.3169</v>
       </c>
       <c r="C71" t="n">
-        <v>176.4343</v>
+        <v>116.5063</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.0583</v>
+        <v>0.0711</v>
       </c>
     </row>
     <row r="72">
@@ -1778,10 +1778,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>9049.135399999999</v>
+        <v>5172.2225</v>
       </c>
       <c r="C72" t="n">
-        <v>180.9827</v>
+        <v>103.4444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.0562</v>
+        <v>0.0709</v>
       </c>
     </row>
     <row r="73">
@@ -1797,10 +1797,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>6927.2965</v>
+        <v>2519.6321</v>
       </c>
       <c r="C73" t="n">
-        <v>138.5459</v>
+        <v>50.3926</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.0536</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="74">
@@ -1816,10 +1816,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>8995.201499999999</v>
+        <v>3772.4599</v>
       </c>
       <c r="C74" t="n">
-        <v>179.904</v>
+        <v>75.4492</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.1628</v>
+        <v>0.2068</v>
       </c>
     </row>
     <row r="75">
@@ -1835,10 +1835,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>11628.2</v>
+        <v>8234.830400000001</v>
       </c>
       <c r="C75" t="n">
-        <v>232.564</v>
+        <v>164.6966</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.0574</v>
+        <v>0.06859999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -1854,10 +1854,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>8544.115100000001</v>
+        <v>5157.9613</v>
       </c>
       <c r="C76" t="n">
-        <v>170.8823</v>
+        <v>103.1592</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.0578</v>
+        <v>0.0701</v>
       </c>
     </row>
     <row r="77">
@@ -1873,10 +1873,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>10454.1779</v>
+        <v>6865.2817</v>
       </c>
       <c r="C77" t="n">
-        <v>209.0836</v>
+        <v>137.3056</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.0612</v>
+        <v>0.0717</v>
       </c>
     </row>
     <row r="78">
@@ -1892,10 +1892,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>9388.2451</v>
+        <v>6385.3239</v>
       </c>
       <c r="C78" t="n">
-        <v>187.7649</v>
+        <v>127.7065</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.1626</v>
+        <v>0.2033</v>
       </c>
     </row>
     <row r="79">
@@ -1911,10 +1911,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>9008.261</v>
+        <v>5250.0191</v>
       </c>
       <c r="C79" t="n">
-        <v>180.1652</v>
+        <v>105.0004</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0583</v>
+        <v>0.0669</v>
       </c>
     </row>
     <row r="80">
@@ -1930,10 +1930,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>9586.858700000001</v>
+        <v>6882.4137</v>
       </c>
       <c r="C80" t="n">
-        <v>191.7372</v>
+        <v>137.6483</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.0602</v>
+        <v>0.0697</v>
       </c>
     </row>
     <row r="81">
@@ -1949,10 +1949,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>9746.0002</v>
+        <v>6993.81</v>
       </c>
       <c r="C81" t="n">
-        <v>194.92</v>
+        <v>139.8762</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.0591</v>
+        <v>0.06859999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -1968,10 +1968,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>7736.0945</v>
+        <v>3427.5526</v>
       </c>
       <c r="C82" t="n">
-        <v>154.7219</v>
+        <v>68.55110000000001</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1614</v>
+        <v>0.1848</v>
       </c>
     </row>
     <row r="83">
@@ -1987,10 +1987,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>7515.4689</v>
+        <v>3506.7395</v>
       </c>
       <c r="C83" t="n">
-        <v>150.3094</v>
+        <v>70.1348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.0574</v>
+        <v>0.0624</v>
       </c>
     </row>
     <row r="84">
@@ -2006,10 +2006,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>8782.6528</v>
+        <v>4929.5252</v>
       </c>
       <c r="C84" t="n">
-        <v>175.6531</v>
+        <v>98.59050000000001</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.0569</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="85">
@@ -2025,10 +2025,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>11019.6834</v>
+        <v>8218.6098</v>
       </c>
       <c r="C85" t="n">
-        <v>220.3937</v>
+        <v>164.3722</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.0587</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="86">
@@ -2044,10 +2044,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>9075.211300000001</v>
+        <v>6416.3423</v>
       </c>
       <c r="C86" t="n">
-        <v>181.5042</v>
+        <v>128.3268</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.1673</v>
+        <v>0.2103</v>
       </c>
     </row>
     <row r="87">
@@ -2063,10 +2063,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>10654.1758</v>
+        <v>7301.8608</v>
       </c>
       <c r="C87" t="n">
-        <v>213.0835</v>
+        <v>146.0372</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.0591</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -2082,10 +2082,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>8250.729499999999</v>
+        <v>3944.0555</v>
       </c>
       <c r="C88" t="n">
-        <v>165.0146</v>
+        <v>78.8811</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.05</v>
+        <v>0.0755</v>
       </c>
     </row>
     <row r="89">
@@ -2101,10 +2101,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>6692.2647</v>
+        <v>1711.7341</v>
       </c>
       <c r="C89" t="n">
-        <v>133.8453</v>
+        <v>34.2347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.0544</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="90">
@@ -2120,10 +2120,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>8359.5692</v>
+        <v>5557.4693</v>
       </c>
       <c r="C90" t="n">
-        <v>167.1914</v>
+        <v>111.1494</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.163</v>
+        <v>0.2056</v>
       </c>
     </row>
     <row r="91">
@@ -2139,10 +2139,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>8239.561600000001</v>
+        <v>4310.2022</v>
       </c>
       <c r="C91" t="n">
-        <v>164.7912</v>
+        <v>86.20399999999999</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.056</v>
+        <v>0.0616</v>
       </c>
     </row>
     <row r="92">
@@ -2158,10 +2158,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>9298.431500000001</v>
+        <v>6655.8485</v>
       </c>
       <c r="C92" t="n">
-        <v>185.9686</v>
+        <v>133.117</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.0595</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -2177,10 +2177,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>11229.1477</v>
+        <v>8278.259899999999</v>
       </c>
       <c r="C93" t="n">
-        <v>224.583</v>
+        <v>165.5652</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.0622</v>
+        <v>0.07389999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -2196,10 +2196,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>7498.9354</v>
+        <v>3208.1122</v>
       </c>
       <c r="C94" t="n">
-        <v>149.9787</v>
+        <v>64.1622</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.162</v>
+        <v>0.2341</v>
       </c>
     </row>
     <row r="95">
@@ -2215,10 +2215,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>6549.7925</v>
+        <v>1552.0819</v>
       </c>
       <c r="C95" t="n">
-        <v>130.9959</v>
+        <v>31.0416</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.053</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="96">
@@ -2234,10 +2234,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>7907.0106</v>
+        <v>4136.4124</v>
       </c>
       <c r="C96" t="n">
-        <v>158.1402</v>
+        <v>82.7282</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.0576</v>
+        <v>0.06710000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -2253,10 +2253,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>12740.0897</v>
+        <v>9454.8886</v>
       </c>
       <c r="C97" t="n">
-        <v>254.8018</v>
+        <v>189.0978</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.0593</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="98">
@@ -2272,10 +2272,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>10372.1331</v>
+        <v>7791.2908</v>
       </c>
       <c r="C98" t="n">
-        <v>207.4427</v>
+        <v>155.8258</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.1651</v>
+        <v>0.2096</v>
       </c>
     </row>
     <row r="99">
@@ -2291,10 +2291,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>9462.5268</v>
+        <v>6958.297</v>
       </c>
       <c r="C99" t="n">
-        <v>189.2505</v>
+        <v>139.1659</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.0616</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="100">
@@ -2310,10 +2310,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>8215.280199999999</v>
+        <v>4138.5355</v>
       </c>
       <c r="C100" t="n">
-        <v>164.3056</v>
+        <v>82.77070000000001</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.0574</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="101">
@@ -2329,10 +2329,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>9085.858099999999</v>
+        <v>5659.2489</v>
       </c>
       <c r="C101" t="n">
-        <v>181.7172</v>
+        <v>113.185</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.0553</v>
+        <v>0.0668</v>
       </c>
     </row>
   </sheetData>
